--- a/Config/Datas/Tables/s_属性方案_AttributeProfileConfig.xlsx
+++ b/Config/Datas/Tables/s_属性方案_AttributeProfileConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbAttributeProfile" sheetId="1" r:id="R3f2400d412a74d3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbAttributeProfile" sheetId="1" r:id="Rf74a2e0043024de2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -494,7 +494,7 @@
         <x:v>玩家闭环调试</x:v>
       </x:c>
       <x:c r="D5" s="31" t="str">
-        <x:v>1:100000;2:20000;3:0;4:400000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:100000;2:20000;3:0;4:400000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="52" customHeight="1">
@@ -506,7 +506,7 @@
         <x:v>近战怪闭环调试</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
-        <x:v>1:40000;2:8000;3:0;4:100000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:40000;2:8000;3:0;4:100000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="52" customHeight="1">
@@ -518,7 +518,7 @@
         <x:v>玩家概率压测</x:v>
       </x:c>
       <x:c r="D7" s="31" t="str">
-        <x:v>1:100000;2:20000;3:0;4:400000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:100000;2:20000;3:0;4:400000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000;15:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="52" customHeight="1">
@@ -530,7 +530,7 @@
         <x:v>近战怪概率压测</x:v>
       </x:c>
       <x:c r="D8" s="31" t="str">
-        <x:v>1:40000;2:8000;3:0;4:100000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:40000;2:8000;3:0;4:100000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000;15:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -542,7 +542,7 @@
         <x:v>M1标准地面怪</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
-        <x:v>1:40000;2:8000;3:0;4:100000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:40000;2:8000;3:0;4:100000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -554,7 +554,7 @@
         <x:v>M1轻型飞行怪</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
-        <x:v>1:30000;2:7000;3:0;4:130000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:30000;2:7000;3:0;4:130000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -566,7 +566,7 @@
         <x:v>M1慢速高血怪</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
-        <x:v>1:65000;2:10000;3:0;4:75000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:65000;2:10000;3:0;4:75000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -578,7 +578,7 @@
         <x:v>M1快速高攻怪</x:v>
       </x:c>
       <x:c r="D12" s="31" t="str">
-        <x:v>1:50000;2:12000;3:0;4:110000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:50000;2:12000;3:0;4:110000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -590,7 +590,123 @@
         <x:v>M1最终Boss</x:v>
       </x:c>
       <x:c r="D13" s="31" t="str">
-        <x:v>1:3000000;2:12000;3:5000;4:80000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:3000000;2:12000;3:5000;4:80000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>游荡者</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>1:35000;2:7000;3:0;4:150000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>坚甲卫</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>1:120000;2:14000;3:8000;4:65000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>追猎者</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>1:45000;2:10000;3:0;4:125000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>重甲卫</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>1:150000;2:18000;3:10000;4:55000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>迅影精英</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>1:900000;2:14000;3:6000;4:150000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>镇域精英</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>1:1600000;2:20000;3:10000;4:70000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="B20" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>磐岳·借劫炼器</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>1:180000;2:20000;3:4000;4:400000;5:900;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="B21" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>周天·借劫炼器</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>1:108000;2:24000;3:1000;4:400000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="B22" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>天劫环境攻击</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>1:1000;2:34000;3:0;4:0;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="B23" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>劫狱执印者</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>1:1800000;2:18000;3:3000;4:105000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000;15:1000</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
